--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2017/KANSAS_2017.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2017/KANSAS_2017.xlsx
@@ -391,7 +391,7 @@
         <v>73</v>
       </c>
       <c r="D2">
-        <v>0.009123859517560305</v>
+        <v>0.009123859517560303</v>
       </c>
     </row>
     <row r="3">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>General Simon Bolivar</t>
+          <t>Gral. Simon Bolivar</t>
         </is>
       </c>
       <c r="C156">
@@ -4974,7 +4974,7 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C257">
@@ -5089,7 +5089,7 @@
         <v>73</v>
       </c>
       <c r="D263">
-        <v>0.009123859517560305</v>
+        <v>0.009123859517560303</v>
       </c>
     </row>
     <row r="264">
@@ -11544,7 +11544,7 @@
       </c>
       <c r="B622" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C622">
